--- a/feedback_forms/030_project_lessons_learned_form--feedback_forms.xlsx
+++ b/feedback_forms/030_project_lessons_learned_form--feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>project_lessons_learned_form</t>
+          <t>project_leads</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Project Leaders</t>
+          <t>Project Leads</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>rating</t>
+          <t>Project Rating</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,17 +561,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>project_outcome_rating</t>
+          <t>lessons_learned</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>outcome_rating</t>
+          <t>Lessons Learned</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>lessons_learned</t>
+          <t>team_feedback</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>lessons_learned</t>
+          <t>Team Feedback</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -617,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>recommendations</t>
+          <t>Recommendations</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>team_feedback</t>
+          <t>project_leads_contact</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>team_feedback</t>
+          <t>Contact Info for Project Leads</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>team_suggestions</t>
+          <t>pmos_contact</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>team_suggestions</t>
+          <t>Contact Info for PMOS</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>project_leads_name</t>
+          <t>project_leads_email</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>project_leads_name</t>
+          <t>Project Leads Email</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>pmos_name</t>
+          <t>pmos_email</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>pmos_name</t>
+          <t>PMOS Email</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>project_leads_contact</t>
+          <t>project_leads_job_title</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>contact_project_leads</t>
+          <t>Job Title</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>pmos_contact</t>
+          <t>pmos_job_title</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>contact_pmos</t>
+          <t>Pmos Job Title</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,17 +768,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>project_leads_email</t>
+          <t>project_leads_department</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>project_leads_email</t>
+          <t>Department</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,17 +791,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>pmos_email</t>
+          <t>pmos_department</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>pmos_email</t>
+          <t>Pmos Department</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -814,17 +814,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>project_leads_job_title</t>
+          <t>project_leads_job_function</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>job_title</t>
+          <t>Job Function</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -837,17 +837,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>pmos_job_title</t>
+          <t>pmos_job_function</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>job_title</t>
+          <t>Pmos Job Function</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>project_leads_department</t>
+          <t>project_leads_manager</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>department</t>
+          <t>Manager</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>pmos_department</t>
+          <t>pmos_manager</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>department</t>
+          <t>Pmos Manager</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -906,17 +906,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>project_leads_job_function</t>
+          <t>project_leads_organisation</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>job_function</t>
+          <t>Organisation</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -929,17 +929,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>pmos_job_function</t>
+          <t>pmos_organisation</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>job_function</t>
+          <t>Pmos Organisation</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -952,17 +952,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>project_leads_manager</t>
+          <t>project_leads_additional_comments</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>manager</t>
+          <t>Additional Comments</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -975,113 +975,21 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>pmos_manager</t>
+          <t>pmos_additional_comments</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>pmos_manager</t>
+          <t>Pmos Additional Comments</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>project_leads_organisation</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>organisation</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>pmos_organisation</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>pmos_organisation</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>project_leads_additional_comments</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>additional_comments</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>pmos_additional_comments</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>pmos_additional_comments</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +1006,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="39" customWidth="1" min="2" max="2"/>
-    <col width="39" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1039,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1056,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1165,369 +1073,318 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>project_outcome_rating_choices</t>
+          <t>team_feedback_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'high'}</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'High'}</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>project_outcome_rating_choices</t>
+          <t>team_feedback_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'low'}</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Low'}</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>project_outcome_rating_choices</t>
+          <t>project_leads_department_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'neutral'}</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Neutral'}</t>
+          <t>Finance</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>team_feedback_choices</t>
+          <t>project_leads_department_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Marketing</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>team_feedback_choices</t>
+          <t>project_leads_department_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sales</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>project_leads_department_choices</t>
+          <t>pmos_department_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'finance'}</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Finance'}</t>
+          <t>Finance</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>project_leads_department_choices</t>
+          <t>pmos_department_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'marketing'}</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Marketing'}</t>
+          <t>Marketing</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>project_leads_department_choices</t>
+          <t>pmos_department_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'sales'}</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Sales'}</t>
+          <t>Sales</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>pmos_department_choices</t>
+          <t>project_leads_job_function_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'finance'}</t>
+          <t>project_manager</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Finance'}</t>
+          <t>Project Manager</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>pmos_department_choices</t>
+          <t>project_leads_job_function_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'marketing'}</t>
+          <t>team_lead</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Marketing'}</t>
+          <t>Team Lead</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>pmos_department_choices</t>
+          <t>project_leads_job_function_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'sales'}</t>
+          <t>team_member</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Sales'}</t>
+          <t>Team Member</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>project_leads_job_function_choices</t>
+          <t>pmos_job_function_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'project_manager'}</t>
+          <t>project_manager</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Project Manager'}</t>
+          <t>Project Manager</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>project_leads_job_function_choices</t>
+          <t>pmos_job_function_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'team_lead'}</t>
+          <t>team_lead</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Team Lead'}</t>
+          <t>Team Lead</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>project_leads_job_function_choices</t>
+          <t>pmos_job_function_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'team_member'}</t>
+          <t>team_member</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Team Member'}</t>
+          <t>Team Member</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>pmos_job_function_choices</t>
+          <t>project_leads_manager_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'project_manager'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Project Manager'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>pmos_job_function_choices</t>
+          <t>project_leads_manager_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'team_lead'}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Team Lead'}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>pmos_job_function_choices</t>
+          <t>pmos_manager_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'team_member'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Team Member'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>project_leads_manager_choices</t>
+          <t>pmos_manager_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>project_leads_manager_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'label':_false}</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'label': False}</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>pmos_manager_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>{'id':_1,_'label':_true}</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>{'id': 1, 'label': True}</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>pmos_manager_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'label':_false}</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
